--- a/artfynd/A 9904-2026 artfynd.xlsx
+++ b/artfynd/A 9904-2026 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132821147</v>
+        <v>132821151</v>
       </c>
       <c r="B2" t="n">
-        <v>79334</v>
+        <v>83343</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572243</v>
+        <v>572225</v>
       </c>
       <c r="R2" t="n">
-        <v>7205095</v>
+        <v>7205017</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132821145</v>
+        <v>132821155</v>
       </c>
       <c r="B3" t="n">
-        <v>79334</v>
+        <v>78393</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572256</v>
+        <v>572208</v>
       </c>
       <c r="R3" t="n">
-        <v>7205128</v>
+        <v>7204955</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,32 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132821160</v>
+        <v>132821150</v>
       </c>
       <c r="B4" t="n">
-        <v>79334</v>
+        <v>78732</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572199</v>
+        <v>572224</v>
       </c>
       <c r="R4" t="n">
-        <v>7204943</v>
+        <v>7205021</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,54 +996,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132821153</v>
+        <v>132821154</v>
       </c>
       <c r="B5" t="n">
-        <v>58332</v>
+        <v>83222</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Vinbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572216</v>
+        <v>572203</v>
       </c>
       <c r="R5" t="n">
-        <v>7204980</v>
+        <v>7204950</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1075,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1085,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,32 +1103,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132821157</v>
+        <v>132821140</v>
       </c>
       <c r="B6" t="n">
-        <v>83316</v>
+        <v>79373</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1147,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>572209</v>
+        <v>572244</v>
       </c>
       <c r="R6" t="n">
-        <v>7204951</v>
+        <v>7205244</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1182,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1192,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1222,11 +1213,11 @@
         <v>132821141</v>
       </c>
       <c r="B7" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1326,50 +1317,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132821146</v>
+        <v>132821145</v>
       </c>
       <c r="B8" t="n">
-        <v>57958</v>
+        <v>79373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Vinbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>572257</v>
+        <v>572256</v>
       </c>
       <c r="R8" t="n">
-        <v>7205129</v>
+        <v>7205128</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1438,50 +1424,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132821144</v>
+        <v>132821147</v>
       </c>
       <c r="B9" t="n">
-        <v>57958</v>
+        <v>79373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Vinbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>572260</v>
+        <v>572243</v>
       </c>
       <c r="R9" t="n">
-        <v>7205143</v>
+        <v>7205095</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1513,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1523,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1553,11 +1534,11 @@
         <v>132821149</v>
       </c>
       <c r="B10" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1657,50 +1638,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132821142</v>
+        <v>132821152</v>
       </c>
       <c r="B11" t="n">
-        <v>57958</v>
+        <v>79373</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Vinbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>572248</v>
+        <v>572228</v>
       </c>
       <c r="R11" t="n">
-        <v>7205228</v>
+        <v>7205012</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1732,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1742,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1769,14 +1745,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132821140</v>
+        <v>132821158</v>
       </c>
       <c r="B12" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1804,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>572244</v>
+        <v>572209</v>
       </c>
       <c r="R12" t="n">
-        <v>7205244</v>
+        <v>7204944</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1839,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1849,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1876,14 +1852,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132821158</v>
+        <v>132821160</v>
       </c>
       <c r="B13" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1911,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>572209</v>
+        <v>572199</v>
       </c>
       <c r="R13" t="n">
-        <v>7204944</v>
+        <v>7204943</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1946,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1956,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1983,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132821154</v>
+        <v>132821157</v>
       </c>
       <c r="B14" t="n">
-        <v>83182</v>
+        <v>83358</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1994,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2018,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>572203</v>
+        <v>572209</v>
       </c>
       <c r="R14" t="n">
-        <v>7204950</v>
+        <v>7204951</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2053,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2063,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2090,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132821151</v>
+        <v>132821161</v>
       </c>
       <c r="B15" t="n">
-        <v>83301</v>
+        <v>57972</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2101,34 +2077,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>306</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Vinbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>572225</v>
+        <v>572198</v>
       </c>
       <c r="R15" t="n">
-        <v>7205017</v>
+        <v>7204939</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2160,7 +2141,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2170,7 +2151,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2197,10 +2178,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132821152</v>
+        <v>132821142</v>
       </c>
       <c r="B16" t="n">
-        <v>79334</v>
+        <v>57975</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2208,34 +2189,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Vinbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>572228</v>
+        <v>572248</v>
       </c>
       <c r="R16" t="n">
-        <v>7205012</v>
+        <v>7205228</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2267,7 +2253,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2277,7 +2263,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2304,10 +2290,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132821156</v>
+        <v>132821143</v>
       </c>
       <c r="B17" t="n">
-        <v>78346</v>
+        <v>57975</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,34 +2301,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Vinbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>572209</v>
+        <v>572254</v>
       </c>
       <c r="R17" t="n">
-        <v>7204951</v>
+        <v>7205224</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2374,7 +2365,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2384,7 +2375,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2411,10 +2402,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132821161</v>
+        <v>132821144</v>
       </c>
       <c r="B18" t="n">
-        <v>57955</v>
+        <v>57975</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2422,16 +2413,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2451,10 +2442,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>572198</v>
+        <v>572260</v>
       </c>
       <c r="R18" t="n">
-        <v>7204939</v>
+        <v>7205143</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2486,7 +2477,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2496,7 +2487,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2523,45 +2514,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132821150</v>
+        <v>132821146</v>
       </c>
       <c r="B19" t="n">
-        <v>78693</v>
+        <v>57975</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>498</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Vinbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>572224</v>
+        <v>572257</v>
       </c>
       <c r="R19" t="n">
-        <v>7205021</v>
+        <v>7205129</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2593,7 +2589,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2603,7 +2599,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2630,27 +2626,27 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132821143</v>
+        <v>132821153</v>
       </c>
       <c r="B20" t="n">
-        <v>57958</v>
+        <v>58349</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2658,10 +2654,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2670,10 +2670,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>572254</v>
+        <v>572216</v>
       </c>
       <c r="R20" t="n">
-        <v>7205224</v>
+        <v>7204980</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2705,7 +2705,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2745,7 +2745,7 @@
         <v>132821159</v>
       </c>
       <c r="B21" t="n">
-        <v>97997</v>
+        <v>98060</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2849,10 +2849,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132821155</v>
+        <v>132821156</v>
       </c>
       <c r="B22" t="n">
-        <v>78357</v>
+        <v>78382</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2860,21 +2860,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>314</v>
+        <v>228579</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2884,10 +2884,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>572208</v>
+        <v>572209</v>
       </c>
       <c r="R22" t="n">
-        <v>7204955</v>
+        <v>7204951</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
